--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CERRO_COLORADO.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CERRO_COLORADO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CERRO_COLORADO</t>
+          <t>CERRO COLORADO</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CERRO_COLORADO.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CERRO_COLORADO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>PERUANO - ITALIANA DOMINGO SAVIO</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-16.38423</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-71.55679000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>768</v>
-      </c>
-      <c r="J2" t="n">
-        <v>60</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-16.38423</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-71.55679</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>40035 V. A. BELAUNDE</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-16.34914</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-71.56077999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1341</v>
-      </c>
-      <c r="J3" t="n">
-        <v>57</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-16.34914</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-71.56078</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1341</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>40044 SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-16.32295</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-71.59307</v>
-      </c>
-      <c r="I4" t="n">
-        <v>642</v>
-      </c>
-      <c r="J4" t="n">
-        <v>29</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-16.32295</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-71.59307</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>40053 MANUEL A. TAPIA FUENTES</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-16.35323</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-71.5673</v>
-      </c>
-      <c r="I5" t="n">
-        <v>446</v>
-      </c>
-      <c r="J5" t="n">
-        <v>23</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-16.35323</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-71.5673</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>40055 ROMEO LUNA VICTORIA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-16.3531</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-71.5647</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1009</v>
-      </c>
-      <c r="J6" t="n">
-        <v>49</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-16.3531</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-71.5647</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>40056 HORACIO ZEBALLOS GAMEZ / 40056 HORACIO ZEVALLOS GAMEZ</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-16.39235</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-71.56704999999999</v>
-      </c>
-      <c r="I7" t="n">
-        <v>655</v>
-      </c>
-      <c r="J7" t="n">
-        <v>35</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-16.39235</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-71.56705</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>40058 IGNACIO ALVAREZ THOMAS</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-16.3807</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-71.5706</v>
-      </c>
-      <c r="I8" t="n">
-        <v>236</v>
-      </c>
-      <c r="J8" t="n">
-        <v>21</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-16.3807</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-71.5706</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>GRAN PACHACUTEC</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-16.3947</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-71.5731</v>
-      </c>
-      <c r="I9" t="n">
-        <v>221</v>
-      </c>
-      <c r="J9" t="n">
-        <v>21</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-16.3947</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-71.5731</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>40061 ESTADO DE SUECIA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-16.3895</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-71.5536</v>
-      </c>
-      <c r="I10" t="n">
-        <v>318</v>
-      </c>
-      <c r="J10" t="n">
-        <v>19</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-16.3895</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-71.5536</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>40103 LIBERTADORES DE AMERICA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-16.351</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-71.57444</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1221</v>
-      </c>
-      <c r="J11" t="n">
-        <v>59</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-16.351</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-71.57444</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>40106 JUAN SANTOS ATAHUALPA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-16.4013</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-71.5686</v>
-      </c>
-      <c r="I12" t="n">
-        <v>364</v>
-      </c>
-      <c r="J12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-16.4013</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-71.5686</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>40671</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-16.335383</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-71.58578300000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>203</v>
-      </c>
-      <c r="J13" t="n">
-        <v>11</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-16.335383</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-71.585783</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>41025 200 MILLAS PERUANAS</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-16.3747</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-71.56229999999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>273</v>
-      </c>
-      <c r="J14" t="n">
-        <v>17</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-16.3747</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-71.5623</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>41026 MARIA MURILLO DE BERNAL</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-16.37716</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-71.56100000000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1116</v>
-      </c>
-      <c r="J15" t="n">
-        <v>54</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-16.37716</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-71.561</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1116</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>CIUDAD MUNICIPAL</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-16.3213</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-71.5917</v>
-      </c>
-      <c r="I16" t="n">
-        <v>212</v>
-      </c>
-      <c r="J16" t="n">
-        <v>9</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-16.3213</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-71.5917</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>40054 JUAN DOMINGO ZAMACOLA Y JAUREGUI</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-16.380238</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-71.562363</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1089</v>
-      </c>
-      <c r="J17" t="n">
-        <v>62</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-16.380238</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-71.562363</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1089</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>LA LIBERTAD</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-16.3801</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-71.56140000000001</v>
-      </c>
-      <c r="I18" t="n">
-        <v>248</v>
-      </c>
-      <c r="J18" t="n">
-        <v>12</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-16.3801</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-71.5614</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>NUESTRA SRA. DE LOS DOLORES</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-16.376657</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-71.56092099999999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>491</v>
-      </c>
-      <c r="J19" t="n">
-        <v>27</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-16.376657</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-71.560921</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>CRISTO MORADO</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-16.31912</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-71.58717</v>
-      </c>
-      <c r="I20" t="n">
-        <v>300</v>
-      </c>
-      <c r="J20" t="n">
-        <v>22</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-16.31912</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-71.58717</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>40677 SAN MIGUEL FEBRES CORDERO</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-16.33506</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-71.58137000000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>597</v>
-      </c>
-      <c r="J21" t="n">
-        <v>30</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-16.33506</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-71.58137</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>40688 JESUCRISTO EL SALVADOR</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-16.329467</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-71.583333</v>
-      </c>
-      <c r="I22" t="n">
-        <v>228</v>
-      </c>
-      <c r="J22" t="n">
-        <v>11</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-16.329467</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-71.583333</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>40689 ALFREDO RODRIGUEZ BALLON</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-16.33095</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-71.58546</v>
-      </c>
-      <c r="I23" t="n">
-        <v>278</v>
-      </c>
-      <c r="J23" t="n">
-        <v>15</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-16.33095</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-71.58546</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>SANTA CATALINA DE SIENA</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-16.3965</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-71.57535</v>
-      </c>
-      <c r="I24" t="n">
-        <v>213</v>
-      </c>
-      <c r="J24" t="n">
-        <v>10</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-16.3965</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-71.57535</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>SANTO TOMAS DE AQUINO</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-16.39352</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-71.56735999999999</v>
-      </c>
-      <c r="I25" t="n">
-        <v>666</v>
-      </c>
-      <c r="J25" t="n">
-        <v>37</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-16.39352</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-71.56736</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>SEÑOR DE HUANCA</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-16.33134</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-71.55329</v>
-      </c>
-      <c r="I26" t="n">
-        <v>411</v>
-      </c>
-      <c r="J26" t="n">
-        <v>18</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-16.33134</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-71.55329</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>JUAN DE LA CRUZ CALIENES</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-16.392125</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-71.5603</v>
-      </c>
-      <c r="I27" t="n">
-        <v>515</v>
-      </c>
-      <c r="J27" t="n">
-        <v>50</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-16.392125</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-71.5603</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>NUESTRA SRA. DE LA ASUNTA</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-16.3533</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-71.56614999999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>614</v>
-      </c>
-      <c r="J28" t="n">
-        <v>35</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-16.3533</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-71.56615</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>SEÑOR DE LA ESPERANZA</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-16.327067</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-71.593767</v>
-      </c>
-      <c r="I29" t="n">
-        <v>235</v>
-      </c>
-      <c r="J29" t="n">
-        <v>18</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-16.327067</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-71.593767</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>SEÑOR DE LAS PIEDADES</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-16.33165</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-71.59224</v>
-      </c>
-      <c r="I30" t="n">
-        <v>225</v>
-      </c>
-      <c r="J30" t="n">
-        <v>19</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-16.33165</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-71.59224</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>NANTERRE</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-16.39386</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-71.56614999999999</v>
-      </c>
-      <c r="I31" t="n">
-        <v>220</v>
-      </c>
-      <c r="J31" t="n">
-        <v>16</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-16.39386</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-71.56615</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>SAN PIO X</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-16.32608</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-71.58414999999999</v>
-      </c>
-      <c r="I32" t="n">
-        <v>746</v>
-      </c>
-      <c r="J32" t="n">
-        <v>28</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-16.32608</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-71.58415</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>40694 CENTRO DE INNOVACION PEDAGOGICA ISPPA</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-16.3133</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-71.60435</v>
-      </c>
-      <c r="I33" t="n">
-        <v>961</v>
-      </c>
-      <c r="J33" t="n">
-        <v>38</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-16.3133</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-71.60435</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>SAN JOSE DE COTTOLENGO</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-16.32878</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-71.57335</v>
-      </c>
-      <c r="I34" t="n">
-        <v>740</v>
-      </c>
-      <c r="J34" t="n">
-        <v>29</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-16.32878</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-71.57335</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>BALMER</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-16.38075</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-71.55365999999999</v>
-      </c>
-      <c r="I35" t="n">
-        <v>346</v>
-      </c>
-      <c r="J35" t="n">
-        <v>14</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-16.38075</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-71.55366</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>40670 EL EDEN FE Y ALEGRIA 51</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-16.3256</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-71.55616999999999</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1169</v>
-      </c>
-      <c r="J36" t="n">
-        <v>60</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-16.3256</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-71.55617</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1169</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>SAN MARCOS - AREQUIPA</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-16.347188</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-71.595719</v>
-      </c>
-      <c r="I37" t="n">
-        <v>316</v>
-      </c>
-      <c r="J37" t="n">
-        <v>14</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-16.347188</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-71.595719</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>NUESTRA SEÑORA DEL DIVINO AMOR</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-16.3743</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-71.56437</v>
-      </c>
-      <c r="I38" t="n">
-        <v>537</v>
-      </c>
-      <c r="J38" t="n">
-        <v>31</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-16.3743</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-71.56437</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>JESUS MAESTRO</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-16.32844</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-71.55571</v>
-      </c>
-      <c r="I39" t="n">
-        <v>298</v>
-      </c>
-      <c r="J39" t="n">
-        <v>18</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-16.32844</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-71.55571</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>VILLA MAGISTERIAL</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-16.32697</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-71.57452000000001</v>
-      </c>
-      <c r="I40" t="n">
-        <v>242</v>
-      </c>
-      <c r="J40" t="n">
-        <v>11</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-16.32697</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-71.57452</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>40173 DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-16.33304</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-71.55849000000001</v>
-      </c>
-      <c r="I41" t="n">
-        <v>239</v>
-      </c>
-      <c r="J41" t="n">
-        <v>10</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-16.33304</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-71.55849</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>40059 ALEJANDRO SANCHEZ ARTEAGA</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-16.39501</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-71.57731</v>
-      </c>
-      <c r="I42" t="n">
-        <v>243</v>
-      </c>
-      <c r="J42" t="n">
-        <v>15</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-16.39501</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-71.57731</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>SAN JUAN APOSTOL</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-16.31222</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-71.54773</v>
-      </c>
-      <c r="I43" t="n">
-        <v>815</v>
-      </c>
-      <c r="J43" t="n">
-        <v>35</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-16.31222</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-71.54773</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>40699 ESCUELA CONCERTADA SOLARIS</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-16.330376</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-71.598484</v>
-      </c>
-      <c r="I44" t="n">
-        <v>389</v>
-      </c>
-      <c r="J44" t="n">
-        <v>14</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-16.330376</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-71.598484</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>40705</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-16.3432</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-71.5954</v>
-      </c>
-      <c r="I45" t="n">
-        <v>649</v>
-      </c>
-      <c r="J45" t="n">
-        <v>30</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-16.3432</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-71.5954</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>SABIO ALFRED BINET</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-16.32944</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-71.58618</v>
-      </c>
-      <c r="I46" t="n">
-        <v>426</v>
-      </c>
-      <c r="J46" t="n">
-        <v>26</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-16.32944</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-71.58618</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>SEÑOR DE LA CAÑA</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-16.33498</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-71.60366999999999</v>
-      </c>
-      <c r="I47" t="n">
-        <v>232</v>
-      </c>
-      <c r="J47" t="n">
-        <v>18</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-16.33498</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-71.60367</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>CASA DE CARIDAD ARTES Y OFICIOS</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-16.329382</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-71.57970899999999</v>
-      </c>
-      <c r="I48" t="n">
-        <v>530</v>
-      </c>
-      <c r="J48" t="n">
-        <v>30</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-16.329382</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-71.579709</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>LITTLE HANDS</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-16.3807</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-71.5591</v>
-      </c>
-      <c r="I49" t="n">
-        <v>42</v>
-      </c>
-      <c r="J49" t="n">
-        <v>3</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-16.3807</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-71.5591</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>SANTO TORIBIO DE MOGROVEJO</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-16.31561</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-71.61069999999999</v>
-      </c>
-      <c r="I50" t="n">
-        <v>405</v>
-      </c>
-      <c r="J50" t="n">
-        <v>14</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-16.31561</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-71.6107</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-16.34</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-71.6046</v>
-      </c>
-      <c r="I51" t="n">
-        <v>579</v>
-      </c>
-      <c r="J51" t="n">
-        <v>32</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-16.34</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-71.6046</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>JOHN FORBES</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-16.3265</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-71.56335</v>
-      </c>
-      <c r="I52" t="n">
-        <v>554</v>
-      </c>
-      <c r="J52" t="n">
-        <v>26</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-16.3265</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-71.56335</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>GRECOS</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-16.32768</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-71.56301000000001</v>
-      </c>
-      <c r="I53" t="n">
-        <v>203</v>
-      </c>
-      <c r="J53" t="n">
-        <v>16</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-16.32768</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-71.56301</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>KINDER BLESSED</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-16.32862</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-71.56247</v>
-      </c>
-      <c r="I54" t="n">
-        <v>250</v>
-      </c>
-      <c r="J54" t="n">
-        <v>14</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-16.32862</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-71.56247</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>LAS PLUMAS DEL AMAUTA</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-16.33937</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-71.61047000000001</v>
-      </c>
-      <c r="I55" t="n">
-        <v>552</v>
-      </c>
-      <c r="J55" t="n">
-        <v>28</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-16.33937</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-71.61047</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>SOR ANA - B</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-16.345608</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-71.617791</v>
-      </c>
-      <c r="I56" t="n">
-        <v>240</v>
-      </c>
-      <c r="J56" t="n">
-        <v>10</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-16.345608</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-71.617791</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>FUTURA SCHOOLS CERRO COLORADO</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-16.36307</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-71.56583000000001</v>
-      </c>
-      <c r="I57" t="n">
-        <v>575</v>
-      </c>
-      <c r="J57" t="n">
-        <v>23</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-16.36307</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-71.56583</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>EL GRAN PODER DE JESUS</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-16.3298</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-71.5926</v>
-      </c>
-      <c r="I58" t="n">
-        <v>210</v>
-      </c>
-      <c r="J58" t="n">
-        <v>19</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-16.3298</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-71.5926</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>DAVID AUSUBEL</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-16.3438</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-71.6078</v>
-      </c>
-      <c r="I59" t="n">
-        <v>212</v>
-      </c>
-      <c r="J59" t="n">
-        <v>19</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-16.3438</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-71.6078</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>TESORO DE JESUS</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-16.35255</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-71.56671</v>
-      </c>
-      <c r="I60" t="n">
-        <v>421</v>
-      </c>
-      <c r="J60" t="n">
-        <v>23</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-16.35255</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-71.56671</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>JUILLIARD</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-16.35156</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-71.56151</v>
-      </c>
-      <c r="I61" t="n">
-        <v>343</v>
-      </c>
-      <c r="J61" t="n">
-        <v>10</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-16.35156</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-71.56151</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>SAN ALFONSO MARIA LIGORIO</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-16.35119</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-71.62178</v>
-      </c>
-      <c r="I62" t="n">
-        <v>209</v>
-      </c>
-      <c r="J62" t="n">
-        <v>9</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-16.35119</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-71.62178</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>LUCERITOS DE DIOS</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-16.356483</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-71.616726</v>
-      </c>
-      <c r="I63" t="n">
-        <v>308</v>
-      </c>
-      <c r="J63" t="n">
-        <v>15</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-16.356483</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-71.616726</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>SANTA ELENITA</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-16.3262</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-71.59121</v>
-      </c>
-      <c r="I64" t="n">
-        <v>34</v>
-      </c>
-      <c r="J64" t="n">
-        <v>5</v>
-      </c>
-      <c r="K64" t="n">
-        <v>1</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-16.3262</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-71.59121</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>JESUS DE NAZARETH</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-16.345889</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-71.612961</v>
-      </c>
-      <c r="I65" t="n">
-        <v>586</v>
-      </c>
-      <c r="J65" t="n">
-        <v>16</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-16.345889</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-71.612961</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>JOULE CIUDAD MUNICIPAL</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-16.32393</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-71.592</v>
-      </c>
-      <c r="I66" t="n">
-        <v>32</v>
-      </c>
-      <c r="J66" t="n">
-        <v>11</v>
-      </c>
-      <c r="K66" t="n">
-        <v>1</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-16.32393</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-71.592</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>JOHN KEYNES</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-16.34396</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-71.6109</v>
-      </c>
-      <c r="I67" t="n">
-        <v>375</v>
-      </c>
-      <c r="J67" t="n">
-        <v>38</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-16.34396</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-71.6109</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>PEQUEÑAS ESTRELLAS</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-16.3757</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-71.5585</v>
-      </c>
-      <c r="I68" t="n">
-        <v>33</v>
-      </c>
-      <c r="J68" t="n">
-        <v>5</v>
-      </c>
-      <c r="K68" t="n">
-        <v>1</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-16.3757</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-71.5585</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>ESTRELLITAS DE AMOR</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-16.332335</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-71.611501</v>
-      </c>
-      <c r="I69" t="n">
-        <v>268</v>
-      </c>
-      <c r="J69" t="n">
-        <v>11</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-16.332335</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-71.611501</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>APIPA SECTOR III</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-16.3272</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-71.60975000000001</v>
-      </c>
-      <c r="I70" t="n">
-        <v>215</v>
-      </c>
-      <c r="J70" t="n">
-        <v>15</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-16.3272</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-71.60975</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>HOLY SCHOOLS</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-16.3234</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-71.604067</v>
-      </c>
-      <c r="I71" t="n">
-        <v>510</v>
-      </c>
-      <c r="J71" t="n">
-        <v>22</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-16.3234</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-71.604067</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>JOHANNES KEPLER</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-16.31367</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-71.6095</v>
-      </c>
-      <c r="I72" t="n">
-        <v>385</v>
-      </c>
-      <c r="J72" t="n">
-        <v>20</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-16.31367</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-71.6095</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>INNOVA SCHOOLS - CERRO COLORADO</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-16.3918</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-71.56468</v>
-      </c>
-      <c r="I73" t="n">
-        <v>1314</v>
-      </c>
-      <c r="J73" t="n">
-        <v>58</v>
-      </c>
-      <c r="K73" t="n">
-        <v>1</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-16.3918</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-71.56468</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>MONTESSORI SCHOOL</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-16.38078</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-71.56227</v>
-      </c>
-      <c r="I74" t="n">
-        <v>582</v>
-      </c>
-      <c r="J74" t="n">
-        <v>51</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-16.38078</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-71.56227</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>DIVINO NIÑO ALTO LIBERTAD</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-16.38003</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-71.57155</v>
-      </c>
-      <c r="I75" t="n">
-        <v>356</v>
-      </c>
-      <c r="J75" t="n">
-        <v>18</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-16.38003</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-71.57155</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>MADRE PEREGRINA SANTISIMA VIRGEN DE CHAPI</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-16.37169</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-71.56223</v>
-      </c>
-      <c r="I76" t="n">
-        <v>468</v>
-      </c>
-      <c r="J76" t="n">
-        <v>26</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-16.37169</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-71.56223</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>ALEXANDER FRIEDMAN</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-16.3248</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-71.593425</v>
-      </c>
-      <c r="I77" t="n">
-        <v>442</v>
-      </c>
-      <c r="J77" t="n">
-        <v>26</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-16.3248</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-71.593425</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>JUILLIARD</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-16.35414</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-71.55937</v>
-      </c>
-      <c r="I78" t="n">
-        <v>394</v>
-      </c>
-      <c r="J78" t="n">
-        <v>9</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-16.35414</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-71.55937</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>MENDEL CERRO COLORADO</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-16.37621</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-71.56117</v>
-      </c>
-      <c r="I79" t="n">
-        <v>603</v>
-      </c>
-      <c r="J79" t="n">
-        <v>21</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-16.37621</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-71.56117</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>TALENT'S SCHOOL AQP</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-16.31572</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-71.55091</v>
-      </c>
-      <c r="I80" t="n">
-        <v>252</v>
-      </c>
-      <c r="J80" t="n">
-        <v>19</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-16.31572</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-71.55091</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>LAS FLORES</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-16.330025</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-71.564981</v>
-      </c>
-      <c r="I81" t="n">
-        <v>300</v>
-      </c>
-      <c r="J81" t="n">
-        <v>18</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-16.330025</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-71.564981</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>PERCY GIBSON MOLLER</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-16.33706</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-71.59448999999999</v>
-      </c>
-      <c r="I82" t="n">
-        <v>227</v>
-      </c>
-      <c r="J82" t="n">
-        <v>23</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-16.33706</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-71.59449</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>CONO NORTE LINUS PAULING</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-16.3285</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-71.60253</v>
-      </c>
-      <c r="I83" t="n">
-        <v>391</v>
-      </c>
-      <c r="J83" t="n">
-        <v>20</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-16.3285</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-71.60253</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>JESUS REDENTOR SCHOOL</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-16.3202</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-71.5912</v>
-      </c>
-      <c r="I84" t="n">
-        <v>49</v>
-      </c>
-      <c r="J84" t="n">
-        <v>5</v>
-      </c>
-      <c r="K84" t="n">
-        <v>1</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-16.3202</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-71.5912</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>BALMER JUVENTUS</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-16.37938</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-71.55968</v>
-      </c>
-      <c r="I85" t="n">
-        <v>315</v>
-      </c>
-      <c r="J85" t="n">
-        <v>18</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-16.37938</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-71.55968</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CERRO_COLORADO.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CERRO_COLORADO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>59081</t>
+          <t>59830</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PERUANO - ITALIANA DOMINGO SAVIO</t>
+          <t>SANTA CATALINA DE SIENA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-16.38423</t>
+          <t>-16.3965</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-71.55679</t>
+          <t>-71.57535</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59383</t>
+          <t>541593</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40035 V. A. BELAUNDE</t>
+          <t>40173 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-16.34914</t>
+          <t>-16.33304</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-71.56078</t>
+          <t>-71.55849</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>239</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>59397</t>
+          <t>680777</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40044 SAN MARTIN DE PORRES</t>
+          <t>SOR ANA - B</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-16.32295</t>
+          <t>-16.345608</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-71.59307</t>
+          <t>-71.617791</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>59401</t>
+          <t>757427</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40053 MANUEL A. TAPIA FUENTES</t>
+          <t>JUILLIARD</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-16.35323</t>
+          <t>-16.35156</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-71.5673</t>
+          <t>-71.56151</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>343</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>59420</t>
+          <t>59552</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40055 ROMEO LUNA VICTORIA</t>
+          <t>40671</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-16.3531</t>
+          <t>-16.335383</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-71.5647</t>
+          <t>-71.585783</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59439</t>
+          <t>59774</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40056 HORACIO ZEBALLOS GAMEZ / 40056 HORACIO ZEVALLOS GAMEZ</t>
+          <t>40688 JESUCRISTO EL SALVADOR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-16.39235</t>
+          <t>-16.329467</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-71.56705</t>
+          <t>-71.583333</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>228</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>59463</t>
+          <t>528515</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>40058 IGNACIO ALVAREZ THOMAS</t>
+          <t>VILLA MAGISTERIAL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-16.3807</t>
+          <t>-16.32697</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-71.5706</t>
+          <t>-71.57452</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>59482</t>
+          <t>786383</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GRAN PACHACUTEC</t>
+          <t>JOULE CIUDAD MUNICIPAL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-16.3947</t>
+          <t>-16.32393</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-71.5731</t>
+          <t>-71.592</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>59496</t>
+          <t>788259</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>40061 ESTADO DE SUECIA</t>
+          <t>ESTRELLITAS DE AMOR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-16.3895</t>
+          <t>-16.332335</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-71.5536</t>
+          <t>-71.611501</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>268</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>59509</t>
+          <t>59670</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>40103 LIBERTADORES DE AMERICA</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-16.351</t>
+          <t>-16.3801</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-71.57444</t>
+          <t>-71.5614</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>248</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>59514</t>
+          <t>278818</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>40106 JUAN SANTOS ATAHUALPA</t>
+          <t>BALMER</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-16.4013</t>
+          <t>-16.38075</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-71.5686</t>
+          <t>-71.55366</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>59552</t>
+          <t>506429</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40671</t>
+          <t>SAN MARCOS - AREQUIPA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-16.335383</t>
+          <t>-16.347188</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-71.585783</t>
+          <t>-71.595719</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>316</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>59566</t>
+          <t>547241</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41025 200 MILLAS PERUANAS</t>
+          <t>40699 ESCUELA CONCERTADA SOLARIS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-16.3747</t>
+          <t>-16.330376</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-71.5623</t>
+          <t>-71.598484</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>389</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>59571</t>
+          <t>619092</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41026 MARIA MURILLO DE BERNAL</t>
+          <t>SANTO TORIBIO DE MOGROVEJO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-16.37716</t>
+          <t>-16.31561</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-71.561</t>
+          <t>-71.6107</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>405</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>59613</t>
+          <t>647995</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CIUDAD MUNICIPAL</t>
+          <t>KINDER BLESSED</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-16.3213</t>
+          <t>-16.32862</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-71.5917</t>
+          <t>-71.56247</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>59665</t>
+          <t>59788</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40054 JUAN DOMINGO ZAMACOLA Y JAUREGUI</t>
+          <t>40689 ALFREDO RODRIGUEZ BALLON</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-16.380238</t>
+          <t>-16.33095</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-71.562363</t>
+          <t>-71.58546</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>278</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>59670</t>
+          <t>546270</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>40059 ALEJANDRO SANCHEZ ARTEAGA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-16.3801</t>
+          <t>-16.39501</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-71.5614</t>
+          <t>-71.57731</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>243</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>59694</t>
+          <t>758865</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NUESTRA SRA. DE LOS DOLORES</t>
+          <t>LUCERITOS DE DIOS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-16.376657</t>
+          <t>-16.356483</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-71.560921</t>
+          <t>-71.616726</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>308</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>59745</t>
+          <t>798588</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CRISTO MORADO</t>
+          <t>APIPA SECTOR III</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-16.31912</t>
+          <t>-16.3272</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-71.58717</t>
+          <t>-71.60975</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>59769</t>
+          <t>60107</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40677 SAN MIGUEL FEBRES CORDERO</t>
+          <t>NANTERRE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-16.33506</t>
+          <t>-16.39386</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-71.58137</t>
+          <t>-71.56615</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>59774</t>
+          <t>638444</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40688 JESUCRISTO EL SALVADOR</t>
+          <t>GRECOS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-16.329467</t>
+          <t>-16.32768</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-71.583333</t>
+          <t>-71.56301</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>59788</t>
+          <t>781253</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40689 ALFREDO RODRIGUEZ BALLON</t>
+          <t>JESUS DE NAZARETH</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-16.33095</t>
+          <t>-16.345889</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-71.58546</t>
+          <t>-71.612961</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>586</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>59830</t>
+          <t>59566</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SANTA CATALINA DE SIENA</t>
+          <t>41025 200 MILLAS PERUANAS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-16.3965</t>
+          <t>-16.3747</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-71.57535</t>
+          <t>-71.5623</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>273</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>59849</t>
+          <t>59854</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SANTO TOMAS DE AQUINO</t>
+          <t>SEÑOR DE HUANCA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-16.39352</t>
+          <t>-16.33134</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-71.56736</t>
+          <t>-71.55329</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>411</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,27 +1989,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>59854</t>
+          <t>60051</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SEÑOR DE HUANCA</t>
+          <t>SEÑOR DE LA ESPERANZA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-16.33134</t>
+          <t>-16.327067</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-71.55329</t>
+          <t>-71.593767</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>235</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>59934</t>
+          <t>522151</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JUAN DE LA CRUZ CALIENES</t>
+          <t>JESUS MAESTRO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-16.392125</t>
+          <t>-16.32844</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-71.5603</t>
+          <t>-71.55571</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>298</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>59972</t>
+          <t>575173</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NUESTRA SRA. DE LA ASUNTA</t>
+          <t>SEÑOR DE LA CAÑA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-16.3533</t>
+          <t>-16.33498</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-71.56615</t>
+          <t>-71.60367</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>232</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2175,27 +2175,27 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>60051</t>
+          <t>828731</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SEÑOR DE LA ESPERANZA</t>
+          <t>DIVINO NIÑO ALTO LIBERTAD</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-16.327067</t>
+          <t>-16.38003</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-71.593767</t>
+          <t>-71.57155</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>356</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>60065</t>
+          <t>863201</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SEÑOR DE LAS PIEDADES</t>
+          <t>LAS FLORES</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-16.33165</t>
+          <t>-16.330025</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-71.59224</t>
+          <t>-71.564981</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>60107</t>
+          <t>998752</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NANTERRE</t>
+          <t>BALMER JUVENTUS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-16.39386</t>
+          <t>-16.37938</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-71.56615</t>
+          <t>-71.55968</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>315</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>60206</t>
+          <t>59496</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SAN PIO X</t>
+          <t>40061 ESTADO DE SUECIA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-16.32608</t>
+          <t>-16.3895</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-71.58415</t>
+          <t>-71.5536</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>318</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>117217</t>
+          <t>59514</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>40694 CENTRO DE INNOVACION PEDAGOGICA ISPPA</t>
+          <t>40106 JUAN SANTOS ATAHUALPA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-16.3133</t>
+          <t>-16.4013</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-71.60435</t>
+          <t>-71.5686</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>364</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>272524</t>
+          <t>60065</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SAN JOSE DE COTTOLENGO</t>
+          <t>SEÑOR DE LAS PIEDADES</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-16.32878</t>
+          <t>-16.33165</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-71.57335</t>
+          <t>-71.59224</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>225</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>278818</t>
+          <t>742153</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>BALMER</t>
+          <t>EL GRAN PODER DE JESUS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-16.38075</t>
+          <t>-16.3298</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-71.55366</t>
+          <t>-71.5926</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>210</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>350908</t>
+          <t>745118</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>40670 EL EDEN FE Y ALEGRIA 51</t>
+          <t>DAVID AUSUBEL</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-16.3256</t>
+          <t>-16.3438</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-71.55617</t>
+          <t>-71.6078</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>506429</t>
+          <t>852132</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SAN MARCOS - AREQUIPA</t>
+          <t>TALENT'S SCHOOL AQP</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-16.347188</t>
+          <t>-16.31572</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-71.595719</t>
+          <t>-71.55091</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>252</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>512604</t>
+          <t>824785</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL DIVINO AMOR</t>
+          <t>JOHANNES KEPLER</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-16.3743</t>
+          <t>-16.31367</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-71.56437</t>
+          <t>-71.6095</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>385</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>522151</t>
+          <t>863932</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JESUS MAESTRO</t>
+          <t>CONO NORTE LINUS PAULING</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-16.32844</t>
+          <t>-16.3285</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-71.55571</t>
+          <t>-71.60253</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>391</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>528515</t>
+          <t>59463</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>VILLA MAGISTERIAL</t>
+          <t>40058 IGNACIO ALVAREZ THOMAS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-16.32697</t>
+          <t>-16.3807</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-71.57452</t>
+          <t>-71.5706</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>236</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>541593</t>
+          <t>59482</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>40173 DIVINO NIÑO JESUS</t>
+          <t>GRAN PACHACUTEC</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-16.33304</t>
+          <t>-16.3947</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-71.55849</t>
+          <t>-71.5731</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>546270</t>
+          <t>849267</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>40059 ALEJANDRO SANCHEZ ARTEAGA</t>
+          <t>MENDEL CERRO COLORADO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-16.39501</t>
+          <t>-16.37621</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-71.57731</t>
+          <t>-71.56117</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>603</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>546661</t>
+          <t>59745</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SAN JUAN APOSTOL</t>
+          <t>CRISTO MORADO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-16.31222</t>
+          <t>-16.31912</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-71.54773</t>
+          <t>-71.58717</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>547241</t>
+          <t>802137</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>40699 ESCUELA CONCERTADA SOLARIS</t>
+          <t>HOLY SCHOOLS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-16.330376</t>
+          <t>-16.3234</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-71.598484</t>
+          <t>-71.604067</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>510</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>547444</t>
+          <t>59401</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>40705</t>
+          <t>40053 MANUEL A. TAPIA FUENTES</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-16.3432</t>
+          <t>-16.35323</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-71.5954</t>
+          <t>-71.5673</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>446</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>573942</t>
+          <t>722598</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SABIO ALFRED BINET</t>
+          <t>FUTURA SCHOOLS CERRO COLORADO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-16.32944</t>
+          <t>-16.36307</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-71.58618</t>
+          <t>-71.56583</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>575</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>575173</t>
+          <t>748145</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SEÑOR DE LA CAÑA</t>
+          <t>TESORO DE JESUS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-16.33498</t>
+          <t>-16.35255</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-71.60367</t>
+          <t>-71.56671</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>421</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>596321</t>
+          <t>863296</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CASA DE CARIDAD ARTES Y OFICIOS</t>
+          <t>PERCY GIBSON MOLLER</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-16.329382</t>
+          <t>-16.33706</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-71.579709</t>
+          <t>-71.59449</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>227</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>597877</t>
+          <t>573942</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LITTLE HANDS</t>
+          <t>SABIO ALFRED BINET</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-16.3807</t>
+          <t>-16.32944</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-71.5591</t>
+          <t>-71.58618</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>426</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>619092</t>
+          <t>630396</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SANTO TORIBIO DE MOGROVEJO</t>
+          <t>JOHN FORBES</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-16.31561</t>
+          <t>-16.3265</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-71.6107</t>
+          <t>-71.56335</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>554</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>627822</t>
+          <t>836496</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
+          <t>MADRE PEREGRINA SANTISIMA VIRGEN DE CHAPI</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-16.37169</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-71.6046</t>
+          <t>-71.56223</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>468</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>630396</t>
+          <t>840889</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>JOHN FORBES</t>
+          <t>ALEXANDER FRIEDMAN</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-16.3265</t>
+          <t>-16.3248</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-71.56335</t>
+          <t>-71.593425</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>442</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>638444</t>
+          <t>59694</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GRECOS</t>
+          <t>NUESTRA SRA. DE LOS DOLORES</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-16.32768</t>
+          <t>-16.376657</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-71.56301</t>
+          <t>-71.560921</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>491</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>647995</t>
+          <t>60206</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>KINDER BLESSED</t>
+          <t>SAN PIO X</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-16.32862</t>
+          <t>-16.32608</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-71.56247</t>
+          <t>-71.58415</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>746</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>680777</t>
+          <t>59397</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SOR ANA - B</t>
+          <t>40044 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-16.345608</t>
+          <t>-16.32295</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-71.617791</t>
+          <t>-71.59307</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>642</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>722598</t>
+          <t>272524</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FUTURA SCHOOLS CERRO COLORADO</t>
+          <t>SAN JOSE DE COTTOLENGO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-16.36307</t>
+          <t>-16.32878</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-71.56583</t>
+          <t>-71.57335</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>740</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>742153</t>
+          <t>597877</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>EL GRAN PODER DE JESUS</t>
+          <t>LITTLE HANDS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-16.3298</t>
+          <t>-16.3807</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-71.5926</t>
+          <t>-71.5591</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>745118</t>
+          <t>59769</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>DAVID AUSUBEL</t>
+          <t>40677 SAN MIGUEL FEBRES CORDERO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-16.3438</t>
+          <t>-16.33506</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-71.6078</t>
+          <t>-71.58137</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>597</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>748145</t>
+          <t>547444</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>TESORO DE JESUS</t>
+          <t>40705</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-16.35255</t>
+          <t>-16.3432</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-71.56671</t>
+          <t>-71.5954</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>649</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>757427</t>
+          <t>596321</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>JUILLIARD</t>
+          <t>CASA DE CARIDAD ARTES Y OFICIOS</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-16.35156</t>
+          <t>-16.329382</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-71.56151</t>
+          <t>-71.579709</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>530</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>758851</t>
+          <t>512604</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SAN ALFONSO MARIA LIGORIO</t>
+          <t>NUESTRA SEÑORA DEL DIVINO AMOR</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-16.35119</t>
+          <t>-16.3743</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-71.62178</t>
+          <t>-71.56437</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>537</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>758865</t>
+          <t>627822</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LUCERITOS DE DIOS</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-16.356483</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-71.616726</t>
+          <t>-71.6046</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>579</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,42 +4345,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>758969</t>
+          <t>59439</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SANTA ELENITA</t>
+          <t>40056 HORACIO ZEBALLOS GAMEZ / 40056 HORACIO ZEVALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-16.3262</t>
+          <t>-16.39235</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-71.59121</t>
+          <t>-71.56705</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>655</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>781253</t>
+          <t>59972</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>JESUS DE NAZARETH</t>
+          <t>NUESTRA SRA. DE LA ASUNTA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-16.345889</t>
+          <t>-16.3533</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-71.612961</t>
+          <t>-71.56615</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>614</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4469,42 +4469,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>786383</t>
+          <t>546661</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>JOULE CIUDAD MUNICIPAL</t>
+          <t>SAN JUAN APOSTOL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-16.32393</t>
+          <t>-16.31222</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-71.592</t>
+          <t>-71.54773</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>815</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>787820</t>
+          <t>59849</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>JOHN KEYNES</t>
+          <t>SANTO TOMAS DE AQUINO</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-16.34396</t>
+          <t>-16.39352</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-71.6109</t>
+          <t>-71.56736</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>666</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4593,37 +4593,37 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>787844</t>
+          <t>117217</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PEQUEÑAS ESTRELLAS</t>
+          <t>40694 CENTRO DE INNOVACION PEDAGOGICA ISPPA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-16.3757</t>
+          <t>-16.3133</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-71.5585</t>
+          <t>-71.60435</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>961</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>788259</t>
+          <t>787820</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ESTRELLITAS DE AMOR</t>
+          <t>JOHN KEYNES</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-16.332335</t>
+          <t>-16.34396</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-71.611501</t>
+          <t>-71.6109</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>375</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>798588</t>
+          <t>59420</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>APIPA SECTOR III</t>
+          <t>40055 ROMEO LUNA VICTORIA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-16.3272</t>
+          <t>-16.3531</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-71.60975</t>
+          <t>-71.5647</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4779,37 +4779,37 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>802137</t>
+          <t>758969</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>HOLY SCHOOLS</t>
+          <t>SANTA ELENITA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-16.3234</t>
+          <t>-16.3262</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-71.604067</t>
+          <t>-71.59121</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4841,37 +4841,37 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>824785</t>
+          <t>787844</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>JOHANNES KEPLER</t>
+          <t>PEQUEÑAS ESTRELLAS</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-16.31367</t>
+          <t>-16.3757</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-71.6095</t>
+          <t>-71.5585</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>825346</t>
+          <t>909807</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CERRO COLORADO</t>
+          <t>JESUS REDENTOR SCHOOL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-16.3918</t>
+          <t>-16.3202</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-71.56468</t>
+          <t>-71.5912</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>827053</t>
+          <t>59934</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MONTESSORI SCHOOL</t>
+          <t>JUAN DE LA CRUZ CALIENES</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-16.38078</t>
+          <t>-16.392125</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-71.56227</t>
+          <t>-71.5603</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>515</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>828731</t>
+          <t>827053</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>DIVINO NIÑO ALTO LIBERTAD</t>
+          <t>MONTESSORI SCHOOL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-16.38003</t>
+          <t>-16.38078</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-71.57155</t>
+          <t>-71.56227</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>582</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>836496</t>
+          <t>59571</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MADRE PEREGRINA SANTISIMA VIRGEN DE CHAPI</t>
+          <t>41026 MARIA MURILLO DE BERNAL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-16.37169</t>
+          <t>-16.37716</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-71.56223</t>
+          <t>-71.561</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>840889</t>
+          <t>59383</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ALEXANDER FRIEDMAN</t>
+          <t>40035 V. A. BELAUNDE</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-16.3248</t>
+          <t>-16.34914</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-71.593425</t>
+          <t>-71.56078</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,37 +5213,37 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>845863</t>
+          <t>825346</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>JUILLIARD</t>
+          <t>INNOVA SCHOOLS - CERRO COLORADO</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-16.35414</t>
+          <t>-16.3918</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-71.55937</t>
+          <t>-71.56468</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>849267</t>
+          <t>59509</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MENDEL CERRO COLORADO</t>
+          <t>40103 LIBERTADORES DE AMERICA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-16.37621</t>
+          <t>-16.351</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-71.56117</t>
+          <t>-71.57444</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>852132</t>
+          <t>59081</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>TALENT'S SCHOOL AQP</t>
+          <t>PERUANO - ITALIANA DOMINGO SAVIO</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-16.31572</t>
+          <t>-16.38423</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-71.55091</t>
+          <t>-71.55679</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>768</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>863201</t>
+          <t>350908</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>LAS FLORES</t>
+          <t>40670 EL EDEN FE Y ALEGRIA 51</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-16.330025</t>
+          <t>-16.3256</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-71.564981</t>
+          <t>-71.55617</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>863296</t>
+          <t>59665</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PERCY GIBSON MOLLER</t>
+          <t>40054 JUAN DOMINGO ZAMACOLA Y JAUREGUI</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-16.33706</t>
+          <t>-16.380238</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-71.59449</t>
+          <t>-71.562363</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,37 +5523,37 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>863932</t>
+          <t>59613</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CONO NORTE LINUS PAULING</t>
+          <t>CIUDAD MUNICIPAL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-16.3285</t>
+          <t>-16.3213</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-71.60253</t>
+          <t>-71.5917</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5585,37 +5585,37 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>909807</t>
+          <t>758851</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>JESUS REDENTOR SCHOOL</t>
+          <t>SAN ALFONSO MARIA LIGORIO</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-16.3202</t>
+          <t>-16.35119</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-71.5912</t>
+          <t>-71.62178</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>209</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>998752</t>
+          <t>845863</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>BALMER JUVENTUS</t>
+          <t>JUILLIARD</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-16.37938</t>
+          <t>-16.35414</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-71.55968</t>
+          <t>-71.55937</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>394</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CERRO_COLORADO.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CERRO_COLORADO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>59830</t>
+          <t>998752</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SANTA CATALINA DE SIENA</t>
+          <t>BALMER JUVENTUS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-16.3965</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-71.57535</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-16.37938</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-71.55968</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>541593</t>
+          <t>909807</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40173 DIVINO NIÑO JESUS</t>
+          <t>JESUS REDENTOR SCHOOL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-16.33304</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-71.55849</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>-16.3202</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-71.5912</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>680777</t>
+          <t>863932</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SOR ANA - B</t>
+          <t>CONO NORTE LINUS PAULING</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-16.345608</t>
+          <t>391</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-71.617791</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>-16.3285</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-71.60253</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>757427</t>
+          <t>863296</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JUILLIARD</t>
+          <t>PERCY GIBSON MOLLER</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-16.35156</t>
+          <t>227</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-71.56151</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>-16.33706</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-71.59449</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>59552</t>
+          <t>863201</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40671</t>
+          <t>LAS FLORES</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-16.335383</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-71.585783</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-16.330025</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-71.564981</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59774</t>
+          <t>852132</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40688 JESUCRISTO EL SALVADOR</t>
+          <t>TALENT'S SCHOOL AQP</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-16.329467</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-71.583333</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>-16.31572</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-71.55091</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>528515</t>
+          <t>849267</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VILLA MAGISTERIAL</t>
+          <t>MENDEL CERRO COLORADO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-16.32697</t>
+          <t>603</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-71.57452</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>-16.37621</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-71.56117</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>786383</t>
+          <t>845863</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JOULE CIUDAD MUNICIPAL</t>
+          <t>JUILLIARD</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-16.32393</t>
+          <t>394</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-71.592</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-16.35414</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-71.55937</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>788259</t>
+          <t>840889</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ESTRELLITAS DE AMOR</t>
+          <t>ALEXANDER FRIEDMAN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-16.332335</t>
+          <t>442</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-71.611501</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>-16.3248</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-71.593425</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>59670</t>
+          <t>836496</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>MADRE PEREGRINA SANTISIMA VIRGEN DE CHAPI</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-16.3801</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-71.5614</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>-16.37169</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-71.56223</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>278818</t>
+          <t>828731</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BALMER</t>
+          <t>DIVINO NIÑO ALTO LIBERTAD</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-16.38075</t>
+          <t>356</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-71.55366</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>-16.38003</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-71.57155</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>506429</t>
+          <t>827053</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SAN MARCOS - AREQUIPA</t>
+          <t>MONTESSORI SCHOOL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-16.347188</t>
+          <t>582</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-71.595719</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>-16.38078</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-71.56227</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>547241</t>
+          <t>825346</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40699 ESCUELA CONCERTADA SOLARIS</t>
+          <t>INNOVA SCHOOLS - CERRO COLORADO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-16.330376</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-71.598484</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>-16.3918</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-71.56468</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>619092</t>
+          <t>824785</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SANTO TORIBIO DE MOGROVEJO</t>
+          <t>JOHANNES KEPLER</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-16.31561</t>
+          <t>385</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-71.6107</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>-16.31367</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-71.6095</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>647995</t>
+          <t>802137</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KINDER BLESSED</t>
+          <t>HOLY SCHOOLS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-16.32862</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-71.56247</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>-16.3234</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-71.604067</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>59788</t>
+          <t>798588</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40689 ALFREDO RODRIGUEZ BALLON</t>
+          <t>APIPA SECTOR III</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-16.33095</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-71.58546</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>-16.3272</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-71.60975</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>546270</t>
+          <t>788259</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40059 ALEJANDRO SANCHEZ ARTEAGA</t>
+          <t>ESTRELLITAS DE AMOR</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-16.39501</t>
+          <t>268</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-71.57731</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>-16.332335</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-71.611501</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,37 +1555,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>758865</t>
+          <t>787844</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>LUCERITOS DE DIOS</t>
+          <t>PEQUEÑAS ESTRELLAS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-16.356483</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-71.616726</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>-16.3757</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-71.5585</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>798588</t>
+          <t>787820</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>APIPA SECTOR III</t>
+          <t>JOHN KEYNES</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-16.3272</t>
+          <t>375</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-71.60975</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>-16.34396</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-71.6109</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>60107</t>
+          <t>786383</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NANTERRE</t>
+          <t>JOULE CIUDAD MUNICIPAL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-16.39386</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-71.56615</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>-16.32393</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-71.592</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>638444</t>
+          <t>781253</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GRECOS</t>
+          <t>JESUS DE NAZARETH</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-16.32768</t>
+          <t>586</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-71.56301</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-16.345889</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-71.612961</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>781253</t>
+          <t>758969</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JESUS DE NAZARETH</t>
+          <t>SANTA ELENITA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-16.345889</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-71.612961</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>-16.3262</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-71.59121</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>59566</t>
+          <t>758865</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>41025 200 MILLAS PERUANAS</t>
+          <t>LUCERITOS DE DIOS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-16.3747</t>
+          <t>308</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-71.5623</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>-16.356483</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-71.616726</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>59854</t>
+          <t>758851</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SEÑOR DE HUANCA</t>
+          <t>SAN ALFONSO MARIA LIGORIO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-16.33134</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-71.55329</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>-16.35119</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-71.62178</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>60051</t>
+          <t>757427</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SEÑOR DE LA ESPERANZA</t>
+          <t>JUILLIARD</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-16.327067</t>
+          <t>343</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-71.593767</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>-16.35156</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-71.56151</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>522151</t>
+          <t>748145</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JESUS MAESTRO</t>
+          <t>TESORO DE JESUS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-16.32844</t>
+          <t>421</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-71.55571</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>-16.35255</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-71.56671</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>575173</t>
+          <t>745118</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SEÑOR DE LA CAÑA</t>
+          <t>DAVID AUSUBEL</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-16.33498</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-71.60367</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>-16.3438</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-71.6078</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>828731</t>
+          <t>742153</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>DIVINO NIÑO ALTO LIBERTAD</t>
+          <t>EL GRAN PODER DE JESUS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-16.38003</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-71.57155</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>-16.3298</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-71.5926</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>863201</t>
+          <t>722598</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>LAS FLORES</t>
+          <t>FUTURA SCHOOLS CERRO COLORADO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-16.330025</t>
+          <t>575</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-71.564981</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>-16.36307</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-71.56583</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>998752</t>
+          <t>680777</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>BALMER JUVENTUS</t>
+          <t>SOR ANA - B</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-16.37938</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-71.55968</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>-16.345608</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-71.617791</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>59496</t>
+          <t>649490</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>40061 ESTADO DE SUECIA</t>
+          <t>LAS PLUMAS DEL AMAUTA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-16.3895</t>
+          <t>552</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-71.5536</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>-16.33937</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-71.61047</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>59514</t>
+          <t>647995</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>40106 JUAN SANTOS ATAHUALPA</t>
+          <t>KINDER BLESSED</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-16.4013</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-71.5686</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>-16.32862</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-71.56247</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>60065</t>
+          <t>638444</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SEÑOR DE LAS PIEDADES</t>
+          <t>GRECOS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-16.33165</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-71.59224</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>-16.32768</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-71.56301</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>742153</t>
+          <t>630396</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>EL GRAN PODER DE JESUS</t>
+          <t>JOHN FORBES</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-16.3298</t>
+          <t>554</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-71.5926</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>-16.3265</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-71.56335</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>745118</t>
+          <t>627822</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>DAVID AUSUBEL</t>
+          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-16.3438</t>
+          <t>579</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-71.6078</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-71.6046</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>852132</t>
+          <t>619092</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TALENT'S SCHOOL AQP</t>
+          <t>SANTO TORIBIO DE MOGROVEJO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-16.31572</t>
+          <t>405</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-71.55091</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>-16.31561</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-71.6107</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>824785</t>
+          <t>597877</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JOHANNES KEPLER</t>
+          <t>LITTLE HANDS</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-16.31367</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-71.6095</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>-16.3807</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-71.5591</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>863932</t>
+          <t>596321</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CONO NORTE LINUS PAULING</t>
+          <t>CASA DE CARIDAD ARTES Y OFICIOS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-16.3285</t>
+          <t>530</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-71.60253</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>-16.329382</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-71.579709</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>59463</t>
+          <t>575173</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>40058 IGNACIO ALVAREZ THOMAS</t>
+          <t>SEÑOR DE LA CAÑA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-16.3807</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-71.5706</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>-16.33498</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-71.60367</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>59482</t>
+          <t>573942</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GRAN PACHACUTEC</t>
+          <t>SABIO ALFRED BINET</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-16.3947</t>
+          <t>426</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-71.5731</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>-16.32944</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-71.58618</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>849267</t>
+          <t>547444</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MENDEL CERRO COLORADO</t>
+          <t>40705</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-16.37621</t>
+          <t>649</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-71.56117</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>-16.3432</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-71.5954</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>59745</t>
+          <t>547241</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CRISTO MORADO</t>
+          <t>40699 ESCUELA CONCERTADA SOLARIS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-16.31912</t>
+          <t>389</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-71.58717</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>-16.330376</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-71.598484</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>802137</t>
+          <t>546661</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>HOLY SCHOOLS</t>
+          <t>SAN JUAN APOSTOL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-16.3234</t>
+          <t>815</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-71.604067</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>-16.31222</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-71.54773</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>59401</t>
+          <t>546270</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>40053 MANUEL A. TAPIA FUENTES</t>
+          <t>40059 ALEJANDRO SANCHEZ ARTEAGA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-16.35323</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-71.5673</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>-16.39501</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-71.57731</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>722598</t>
+          <t>541593</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FUTURA SCHOOLS CERRO COLORADO</t>
+          <t>40173 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-16.36307</t>
+          <t>239</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-71.56583</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>-16.33304</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-71.55849</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>748145</t>
+          <t>528515</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TESORO DE JESUS</t>
+          <t>VILLA MAGISTERIAL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-16.35255</t>
+          <t>242</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-71.56671</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>-16.32697</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-71.57452</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>863296</t>
+          <t>522151</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>PERCY GIBSON MOLLER</t>
+          <t>JESUS MAESTRO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-16.33706</t>
+          <t>298</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-71.59449</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>-16.32844</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-71.55571</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>573942</t>
+          <t>512604</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SABIO ALFRED BINET</t>
+          <t>NUESTRA SEÑORA DEL DIVINO AMOR</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-16.32944</t>
+          <t>537</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-71.58618</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>-16.3743</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-71.56437</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>630396</t>
+          <t>506429</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>JOHN FORBES</t>
+          <t>SAN MARCOS - AREQUIPA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-16.3265</t>
+          <t>316</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-71.56335</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>-16.347188</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-71.595719</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>836496</t>
+          <t>350908</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MADRE PEREGRINA SANTISIMA VIRGEN DE CHAPI</t>
+          <t>40670 EL EDEN FE Y ALEGRIA 51</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-16.37169</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-71.56223</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>-16.3256</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-71.55617</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>840889</t>
+          <t>278818</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ALEXANDER FRIEDMAN</t>
+          <t>BALMER</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-16.3248</t>
+          <t>346</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-71.593425</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>-16.38075</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-71.55366</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>59694</t>
+          <t>272524</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>NUESTRA SRA. DE LOS DOLORES</t>
+          <t>SAN JOSE DE COTTOLENGO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-16.376657</t>
+          <t>740</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-71.560921</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>-16.32878</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-71.57335</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>60206</t>
+          <t>117217</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SAN PIO X</t>
+          <t>40694 CENTRO DE INNOVACION PEDAGOGICA ISPPA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-16.32608</t>
+          <t>961</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-71.58415</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>-16.3133</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-71.60435</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>649490</t>
+          <t>060206</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LAS PLUMAS DEL AMAUTA</t>
+          <t>SAN PIO X</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-16.33937</t>
+          <t>746</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-71.61047</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>-16.32608</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-71.58415</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>59397</t>
+          <t>060107</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>40044 SAN MARTIN DE PORRES</t>
+          <t>NANTERRE</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-16.32295</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-71.59307</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>-16.39386</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-71.56615</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>272524</t>
+          <t>060065</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SAN JOSE DE COTTOLENGO</t>
+          <t>SEÑOR DE LAS PIEDADES</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-16.32878</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-71.57335</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>-16.33165</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-71.59224</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>597877</t>
+          <t>060051</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>LITTLE HANDS</t>
+          <t>SEÑOR DE LA ESPERANZA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-16.3807</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-71.5591</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-16.327067</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-71.593767</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>59769</t>
+          <t>059972</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>40677 SAN MIGUEL FEBRES CORDERO</t>
+          <t>NUESTRA SRA. DE LA ASUNTA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-16.33506</t>
+          <t>614</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-71.58137</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>-16.3533</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-71.56615</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>547444</t>
+          <t>059934</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>40705</t>
+          <t>JUAN DE LA CRUZ CALIENES</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-16.3432</t>
+          <t>515</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-71.5954</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>-16.392125</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-71.5603</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>596321</t>
+          <t>059854</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CASA DE CARIDAD ARTES Y OFICIOS</t>
+          <t>SEÑOR DE HUANCA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-16.329382</t>
+          <t>411</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-71.579709</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>-16.33134</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-71.55329</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>512604</t>
+          <t>059849</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL DIVINO AMOR</t>
+          <t>SANTO TOMAS DE AQUINO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-16.3743</t>
+          <t>666</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-71.56437</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>-16.39352</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-71.56736</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>627822</t>
+          <t>059830</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
+          <t>SANTA CATALINA DE SIENA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-71.6046</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>-16.3965</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-71.57535</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>59439</t>
+          <t>059788</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>40056 HORACIO ZEBALLOS GAMEZ / 40056 HORACIO ZEVALLOS GAMEZ</t>
+          <t>40689 ALFREDO RODRIGUEZ BALLON</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-16.39235</t>
+          <t>278</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-71.56705</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>-16.33095</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-71.58546</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>59972</t>
+          <t>059774</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NUESTRA SRA. DE LA ASUNTA</t>
+          <t>40688 JESUCRISTO EL SALVADOR</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-16.3533</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-71.56615</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>-16.329467</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-71.583333</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>546661</t>
+          <t>059769</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SAN JUAN APOSTOL</t>
+          <t>40677 SAN MIGUEL FEBRES CORDERO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-16.31222</t>
+          <t>597</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-71.54773</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>-16.33506</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-71.58137</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>59849</t>
+          <t>059745</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SANTO TOMAS DE AQUINO</t>
+          <t>CRISTO MORADO</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-16.39352</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-71.56736</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>-16.31912</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-71.58717</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>117217</t>
+          <t>059694</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>40694 CENTRO DE INNOVACION PEDAGOGICA ISPPA</t>
+          <t>NUESTRA SRA. DE LOS DOLORES</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-16.3133</t>
+          <t>491</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-71.60435</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>-16.376657</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-71.560921</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>787820</t>
+          <t>059670</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>JOHN KEYNES</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-16.34396</t>
+          <t>248</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-71.6109</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>-16.3801</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-71.5614</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>59420</t>
+          <t>059665</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>40055 ROMEO LUNA VICTORIA</t>
+          <t>40054 JUAN DOMINGO ZAMACOLA Y JAUREGUI</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-16.3531</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-71.5647</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>-16.380238</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-71.562363</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>758969</t>
+          <t>059613</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SANTA ELENITA</t>
+          <t>CIUDAD MUNICIPAL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-16.3262</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-71.59121</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-16.3213</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-71.5917</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,37 +4841,37 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>787844</t>
+          <t>059571</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PEQUEÑAS ESTRELLAS</t>
+          <t>41026 MARIA MURILLO DE BERNAL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-16.3757</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-71.5585</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-16.37716</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-71.561</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4903,37 +4903,37 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>909807</t>
+          <t>059566</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>JESUS REDENTOR SCHOOL</t>
+          <t>41025 200 MILLAS PERUANAS</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-16.3202</t>
+          <t>273</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-71.5912</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-16.3747</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-71.5623</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>59934</t>
+          <t>059552</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>JUAN DE LA CRUZ CALIENES</t>
+          <t>40671</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-16.392125</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-71.5603</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>-16.335383</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-71.585783</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>827053</t>
+          <t>059514</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MONTESSORI SCHOOL</t>
+          <t>40106 JUAN SANTOS ATAHUALPA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-16.38078</t>
+          <t>364</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-71.56227</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>-16.4013</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-71.5686</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>59571</t>
+          <t>059509</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>41026 MARIA MURILLO DE BERNAL</t>
+          <t>40103 LIBERTADORES DE AMERICA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-16.37716</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-71.561</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>-16.351</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-71.57444</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>59383</t>
+          <t>059496</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>40035 V. A. BELAUNDE</t>
+          <t>40061 ESTADO DE SUECIA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-16.34914</t>
+          <t>318</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-71.56078</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>-16.3895</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-71.5536</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5213,37 +5213,37 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>825346</t>
+          <t>059482</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CERRO COLORADO</t>
+          <t>GRAN PACHACUTEC</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-16.3918</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-71.56468</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>-16.3947</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-71.5731</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>59509</t>
+          <t>059463</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>40103 LIBERTADORES DE AMERICA</t>
+          <t>40058 IGNACIO ALVAREZ THOMAS</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-16.351</t>
+          <t>236</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-71.57444</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>-16.3807</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-71.5706</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>59081</t>
+          <t>059439</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PERUANO - ITALIANA DOMINGO SAVIO</t>
+          <t>40056 HORACIO ZEBALLOS GAMEZ / 40056 HORACIO ZEVALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-16.38423</t>
+          <t>655</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-71.55679</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>-16.39235</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-71.56705</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>350908</t>
+          <t>059420</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>40670 EL EDEN FE Y ALEGRIA 51</t>
+          <t>40055 ROMEO LUNA VICTORIA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-16.3256</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-71.55617</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>-16.3531</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-71.5647</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>59665</t>
+          <t>059401</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>40054 JUAN DOMINGO ZAMACOLA Y JAUREGUI</t>
+          <t>40053 MANUEL A. TAPIA FUENTES</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-16.380238</t>
+          <t>446</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-71.562363</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>-16.35323</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-71.5673</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,37 +5523,37 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>59613</t>
+          <t>059397</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CIUDAD MUNICIPAL</t>
+          <t>40044 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-16.3213</t>
+          <t>642</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-71.5917</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>-16.32295</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-71.59307</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>758851</t>
+          <t>059383</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SAN ALFONSO MARIA LIGORIO</t>
+          <t>40035 V. A. BELAUNDE</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-16.35119</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-71.62178</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-16.34914</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-71.56078</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>845863</t>
+          <t>059081</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>JUILLIARD</t>
+          <t>PERUANO - ITALIANA DOMINGO SAVIO</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-16.35414</t>
+          <t>768</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-71.55937</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>-16.38423</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-71.55679</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CERRO_COLORADO.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-CERRO_COLORADO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
